--- a/artfynd/A 3784-2025 artfynd.xlsx
+++ b/artfynd/A 3784-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2441,130 +2441,6 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>77133213</v>
-      </c>
-      <c r="B17" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>205976</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Gråkråka</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Corvus corone cornix</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Lundboskär rast-/busshållplats, Grannäsfjärden, Srm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>613044.4081312127</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6598634.96524949</v>
-      </c>
-      <c r="S17" t="n">
-        <v>45</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Strängnäs</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Aspö</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2019-04-19</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>08:58</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2019-04-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Ulf Persson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Ulf Persson, Anita Markusson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3784-2025 artfynd.xlsx
+++ b/artfynd/A 3784-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>26519381</v>
+        <v>34870090</v>
       </c>
       <c r="B2" t="n">
-        <v>56671</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103006</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rörsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Acrocephalus scirpaceus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hermann, 1804)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +708,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lundboskär rast-/busshållplats, Grannäsfjärden, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613044.4081312127</v>
+        <v>613044</v>
       </c>
       <c r="R2" t="n">
-        <v>6598634.96524949</v>
+        <v>6598635</v>
       </c>
       <c r="S2" t="n">
         <v>45</v>
@@ -754,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-05-15</t>
+          <t>1997-05-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-05-15</t>
+          <t>1997-05-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,12 +774,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo Nensén</t>
+          <t>Stefan Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo Nensén</t>
+          <t>Stefan Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -799,16 +789,11 @@
         <v>31760445</v>
       </c>
       <c r="B3" t="n">
-        <v>56310</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -845,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613044.4081312127</v>
+        <v>613044</v>
       </c>
       <c r="R3" t="n">
-        <v>6598634.96524949</v>
+        <v>6598635</v>
       </c>
       <c r="S3" t="n">
         <v>45</v>
@@ -917,32 +902,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>34870090</v>
+        <v>46782465</v>
       </c>
       <c r="B4" t="n">
-        <v>56400</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>100096</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -961,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613044.4081312127</v>
+        <v>613044</v>
       </c>
       <c r="R4" t="n">
-        <v>6598634.96524949</v>
+        <v>6598635</v>
       </c>
       <c r="S4" t="n">
         <v>45</v>
@@ -991,22 +971,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1997-05-29</t>
+          <t>2013-07-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1997-05-29</t>
+          <t>2013-07-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,66 +1001,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Stefan Karlsson</t>
+          <t>B Peter Fridén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Karlsson</t>
+          <t>B Peter Fridén, Barbro Hellström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>41394556</v>
+        <v>70904501</v>
       </c>
       <c r="B5" t="n">
-        <v>56521</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103035</v>
+        <v>102952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lundboskär rast-/busshållplats, Grannäsfjärden, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613044.4081312127</v>
+        <v>613044</v>
       </c>
       <c r="R5" t="n">
-        <v>6598634.96524949</v>
+        <v>6598635</v>
       </c>
       <c r="S5" t="n">
         <v>45</v>
@@ -1107,22 +1081,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-01-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>08:20</t>
+          <t>2018-04-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-01-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2018-04-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,27 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ingrid Åkerberg</t>
+          <t>Arvid Landgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ingrid Åkerberg</t>
+          <t>Arvid Landgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>41399080</v>
+        <v>53669766</v>
       </c>
       <c r="B6" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57546</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,16 +1124,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>102963</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1184,7 +1143,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1193,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613044.4081312127</v>
+        <v>613044</v>
       </c>
       <c r="R6" t="n">
-        <v>6598634.96524949</v>
+        <v>6598635</v>
       </c>
       <c r="S6" t="n">
         <v>45</v>
@@ -1223,22 +1189,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-01-29</t>
+          <t>2015-05-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-01-29</t>
+          <t>2015-05-27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,59 +1219,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ingrid Åkerberg</t>
+          <t>Roland Thuvander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ingrid Åkerberg</t>
+          <t>Roland Thuvander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>42782234</v>
+        <v>42791558</v>
       </c>
       <c r="B7" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103018</v>
+        <v>102976</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1314,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613044.4081312127</v>
+        <v>613044</v>
       </c>
       <c r="R7" t="n">
-        <v>6598634.96524949</v>
+        <v>6598635</v>
       </c>
       <c r="S7" t="n">
         <v>45</v>
@@ -1386,42 +1342,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>42791558</v>
+        <v>48469447</v>
       </c>
       <c r="B8" t="n">
-        <v>55667</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102976</v>
+        <v>102977</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1430,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613044.4081312127</v>
+        <v>613044</v>
       </c>
       <c r="R8" t="n">
-        <v>6598634.96524949</v>
+        <v>6598635</v>
       </c>
       <c r="S8" t="n">
         <v>45</v>
@@ -1460,22 +1416,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2012-05-27</t>
+          <t>2014-03-09</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2012-05-27</t>
+          <t>2014-03-09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,42 +1458,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>48467896</v>
+        <v>26522355</v>
       </c>
       <c r="B9" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103042</v>
+        <v>102980</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1546,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613044.4081312127</v>
+        <v>613044</v>
       </c>
       <c r="R9" t="n">
-        <v>6598634.96524949</v>
+        <v>6598635</v>
       </c>
       <c r="S9" t="n">
         <v>45</v>
@@ -1576,22 +1532,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-03-09</t>
+          <t>2007-05-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-03-09</t>
+          <t>2007-05-15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,27 +1562,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ingrid Åkerberg</t>
+          <t>Bo Nensén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ingrid Åkerberg</t>
+          <t>Bo Nensén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>53669766</v>
+        <v>70904546</v>
       </c>
       <c r="B10" t="n">
-        <v>55946</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,45 +1585,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102963</v>
+        <v>102987</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lundboskär rast-/busshållplats, Grannäsfjärden, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613044.4081312127</v>
+        <v>613044</v>
       </c>
       <c r="R10" t="n">
-        <v>6598634.96524949</v>
+        <v>6598635</v>
       </c>
       <c r="S10" t="n">
         <v>45</v>
@@ -1699,22 +1646,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2015-05-27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2018-04-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2015-05-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2018-04-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,61 +1666,54 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Roland Thuvander</t>
+          <t>Arvid Landgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roland Thuvander</t>
+          <t>Arvid Landgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>53669774</v>
+        <v>26515757</v>
       </c>
       <c r="B11" t="n">
-        <v>55981</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58420</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102964</v>
+        <v>102992</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Näktergal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Luscinia luscinia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1792,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613044.4081312127</v>
+        <v>613044</v>
       </c>
       <c r="R11" t="n">
-        <v>6598634.96524949</v>
+        <v>6598635</v>
       </c>
       <c r="S11" t="n">
         <v>45</v>
@@ -1822,22 +1752,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2015-05-27</t>
+          <t>2007-05-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2015-05-27</t>
+          <t>2007-05-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,44 +1782,39 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Roland Thuvander</t>
+          <t>Bo Nensén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Roland Thuvander</t>
+          <t>Bo Nensén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>70904494</v>
+        <v>70904572</v>
       </c>
       <c r="B12" t="n">
-        <v>56779</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103037</v>
+        <v>102999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1907,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613044.4081312127</v>
+        <v>613044</v>
       </c>
       <c r="R12" t="n">
-        <v>6598634.96524949</v>
+        <v>6598635</v>
       </c>
       <c r="S12" t="n">
         <v>45</v>
@@ -1940,19 +1865,9 @@
           <t>2018-04-26</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2018-04-26</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,12 +1897,7 @@
         <v>70904468</v>
       </c>
       <c r="B13" t="n">
-        <v>56806</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613044.4081312127</v>
+        <v>613044</v>
       </c>
       <c r="R13" t="n">
-        <v>6598634.96524949</v>
+        <v>6598635</v>
       </c>
       <c r="S13" t="n">
         <v>45</v>
@@ -2055,19 +1965,9 @@
           <t>2018-04-26</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2018-04-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2094,15 +1994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>70904572</v>
+        <v>26519381</v>
       </c>
       <c r="B14" t="n">
-        <v>56812</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2110,37 +2005,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102999</v>
+        <v>103006</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rörsångare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Acrocephalus scirpaceus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+          <t>(Hermann, 1804)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundboskär rast-/busshållplats, Grannäsfjärden, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613044.4081312127</v>
+        <v>613044</v>
       </c>
       <c r="R14" t="n">
-        <v>6598634.96524949</v>
+        <v>6598635</v>
       </c>
       <c r="S14" t="n">
         <v>45</v>
@@ -2167,22 +2068,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>2007-05-15</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>2007-05-15</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,69 +2098,66 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Arvid Landgren</t>
+          <t>Bo Nensén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Arvid Landgren</t>
+          <t>Bo Nensén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>70904486</v>
+        <v>48467537</v>
       </c>
       <c r="B15" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103055</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lundboskär rast-/busshållplats, Grannäsfjärden, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613044.4081312127</v>
+        <v>613044</v>
       </c>
       <c r="R15" t="n">
-        <v>6598634.96524949</v>
+        <v>6598635</v>
       </c>
       <c r="S15" t="n">
         <v>45</v>
@@ -2286,22 +2184,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>2014-03-09</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>2014-03-09</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2316,65 +2214,66 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Arvid Landgren</t>
+          <t>Ingrid Åkerberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Arvid Landgren</t>
+          <t>Ingrid Åkerberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>70904501</v>
+        <v>42782234</v>
       </c>
       <c r="B16" t="n">
-        <v>55803</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102952</v>
+        <v>103018</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundboskär rast-/busshållplats, Grannäsfjärden, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613044.4081312127</v>
+        <v>613044</v>
       </c>
       <c r="R16" t="n">
-        <v>6598634.96524949</v>
+        <v>6598635</v>
       </c>
       <c r="S16" t="n">
         <v>45</v>
@@ -2401,22 +2300,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>2012-05-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>2012-05-27</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,15 +2330,663 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Ingrid Åkerberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ingrid Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>41399080</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lundboskär rast-/busshållplats, Grannäsfjärden, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>613044</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6598635</v>
+      </c>
+      <c r="S17" t="n">
+        <v>45</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Aspö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2012-01-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2012-01-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ingrid Åkerberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ingrid Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>70904494</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lundboskär rast-/busshållplats, Grannäsfjärden, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>613044</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6598635</v>
+      </c>
+      <c r="S18" t="n">
+        <v>45</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Aspö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2018-04-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2018-04-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Arvid Landgren</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Arvid Landgren</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>48467896</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lundboskär rast-/busshållplats, Grannäsfjärden, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>613044</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6598635</v>
+      </c>
+      <c r="S19" t="n">
+        <v>45</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Aspö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2014-03-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2014-03-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ingrid Åkerberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ingrid Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>41386268</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lundboskär rast-/busshållplats, Grannäsfjärden, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>613044</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6598635</v>
+      </c>
+      <c r="S20" t="n">
+        <v>45</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Aspö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2012-01-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2012-01-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ingrid Åkerberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ingrid Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>70904486</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lundboskär rast-/busshållplats, Grannäsfjärden, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>613044</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6598635</v>
+      </c>
+      <c r="S21" t="n">
+        <v>45</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Aspö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2018-04-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2018-04-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Arvid Landgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Arvid Landgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>41394556</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lundboskär rast-/busshållplats, Grannäsfjärden, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>613044</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6598635</v>
+      </c>
+      <c r="S22" t="n">
+        <v>45</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Aspö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2012-01-29</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2012-01-29</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ingrid Åkerberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ingrid Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3784-2025 artfynd.xlsx
+++ b/artfynd/A 3784-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/34870090</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/31760445</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/46782465</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70904501</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,6 +1253,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53669766</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/42791558</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1455,6 +1490,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/48469447</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1571,6 +1611,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26522355</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,6 +1720,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70904546</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1791,6 +1841,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26515757</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1891,6 +1946,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70904572</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1991,6 +2051,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70904468</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2107,6 +2172,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26519381</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2223,6 +2293,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/48467537</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2339,6 +2414,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/42782234</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2450,6 +2530,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/41399080</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2550,6 +2635,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70904494</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2661,6 +2751,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/48467896</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2772,6 +2867,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/41386268</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2876,6 +2976,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70904486</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2987,8 +3092,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/41394556</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>